--- a/research/traditional_assets/database/data/egypt/egypt_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.163</v>
+        <v>0.073</v>
       </c>
       <c r="E2">
-        <v>0.168</v>
-      </c>
-      <c r="F2">
-        <v>0.11</v>
+        <v>0.0348</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>116.1</v>
+        <v>25.1</v>
       </c>
       <c r="L2">
-        <v>0.3469814704124328</v>
+        <v>0.233923578751165</v>
       </c>
       <c r="M2">
-        <v>16.62</v>
+        <v>4.59</v>
       </c>
       <c r="N2">
-        <v>0.04421388667198724</v>
+        <v>0.01893564356435644</v>
       </c>
       <c r="O2">
-        <v>0.1431524547803618</v>
+        <v>0.1828685258964143</v>
       </c>
       <c r="P2">
-        <v>16.62</v>
+        <v>4.59</v>
       </c>
       <c r="Q2">
-        <v>0.04421388667198724</v>
+        <v>0.01893564356435644</v>
       </c>
       <c r="R2">
-        <v>0.1431524547803618</v>
+        <v>0.1828685258964143</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1890</v>
+        <v>674.4</v>
       </c>
       <c r="V2">
-        <v>5.027932960893855</v>
+        <v>2.782178217821782</v>
       </c>
       <c r="W2">
-        <v>0.1880241831407363</v>
+        <v>0.07150997150997151</v>
       </c>
       <c r="X2">
-        <v>0.08792800286215768</v>
+        <v>0.09631671204813229</v>
       </c>
       <c r="Y2">
-        <v>0.1000961802785786</v>
+        <v>-0.02480674053816077</v>
       </c>
       <c r="Z2">
-        <v>-1.262641509433962</v>
+        <v>5.58854166666667</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08205414384422233</v>
+        <v>0.09637266331478112</v>
       </c>
       <c r="AC2">
-        <v>-0.08205414384422233</v>
+        <v>-0.09637266331478112</v>
       </c>
       <c r="AD2">
-        <v>78.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>78.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG2">
-        <v>-1811.6</v>
+        <v>-664.4</v>
       </c>
       <c r="AH2">
-        <v>0.1725731895223421</v>
+        <v>0.03961965134706814</v>
       </c>
       <c r="AI2">
-        <v>0.09640924741760946</v>
+        <v>0.03544842254519674</v>
       </c>
       <c r="AJ2">
-        <v>1.261823500731351</v>
+        <v>1.574407582938389</v>
       </c>
       <c r="AK2">
-        <v>1.682392273402675</v>
+        <v>1.693601835330105</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.164</v>
+        <v>0.073</v>
       </c>
       <c r="E3">
-        <v>0.126</v>
+        <v>0.0348</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>42.7</v>
+        <v>25.1</v>
       </c>
       <c r="L3">
-        <v>0.2420634920634921</v>
+        <v>0.233923578751165</v>
       </c>
       <c r="M3">
-        <v>5.32</v>
+        <v>4.59</v>
       </c>
       <c r="N3">
-        <v>0.02995495495495496</v>
+        <v>0.01893564356435644</v>
       </c>
       <c r="O3">
-        <v>0.1245901639344262</v>
+        <v>0.1828685258964143</v>
       </c>
       <c r="P3">
-        <v>5.32</v>
+        <v>4.59</v>
       </c>
       <c r="Q3">
-        <v>0.02995495495495496</v>
+        <v>0.01893564356435644</v>
       </c>
       <c r="R3">
-        <v>0.1245901639344262</v>
+        <v>0.1828685258964143</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,185 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>100.9</v>
+        <v>674.4</v>
       </c>
       <c r="V3">
-        <v>0.5681306306306306</v>
+        <v>2.782178217821782</v>
       </c>
       <c r="W3">
-        <v>0.1404143373890168</v>
+        <v>0.07150997150997151</v>
       </c>
       <c r="X3">
-        <v>0.08153361873818123</v>
+        <v>0.09631671204813229</v>
       </c>
       <c r="Y3">
-        <v>0.05888071865083554</v>
+        <v>-0.02480674053816077</v>
       </c>
       <c r="Z3">
-        <v>1.461474730737365</v>
+        <v>5.58854166666667</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07974827885892521</v>
+        <v>0.09637266331478112</v>
       </c>
       <c r="AC3">
-        <v>-0.07974827885892521</v>
+        <v>-0.09637266331478112</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AG3">
-        <v>-88.40000000000001</v>
+        <v>-664.4</v>
       </c>
       <c r="AH3">
-        <v>0.06575486586007365</v>
+        <v>0.03961965134706814</v>
       </c>
       <c r="AI3">
-        <v>0.03372908796546141</v>
+        <v>0.03544842254519674</v>
       </c>
       <c r="AJ3">
-        <v>-0.9910313901345293</v>
+        <v>1.574407582938389</v>
       </c>
       <c r="AK3">
-        <v>-0.3277715980719317</v>
+        <v>1.693601835330105</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>alBaraka Bank Egypt S.A.E. (CASE:SAUD)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.162</v>
-      </c>
-      <c r="E4">
-        <v>0.21</v>
-      </c>
-      <c r="F4">
-        <v>0.11</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="L4">
-        <v>0.4639696586599242</v>
-      </c>
-      <c r="M4">
-        <v>11.3</v>
-      </c>
-      <c r="N4">
-        <v>0.05698436712052446</v>
-      </c>
-      <c r="O4">
-        <v>0.1539509536784741</v>
-      </c>
-      <c r="P4">
-        <v>11.3</v>
-      </c>
-      <c r="Q4">
-        <v>0.05698436712052446</v>
-      </c>
-      <c r="R4">
-        <v>0.1539509536784741</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1789.1</v>
-      </c>
-      <c r="V4">
-        <v>9.022188603126574</v>
-      </c>
-      <c r="W4">
-        <v>0.2356340288924559</v>
-      </c>
-      <c r="X4">
-        <v>0.09432238698613414</v>
-      </c>
-      <c r="Y4">
-        <v>0.1413116419063217</v>
-      </c>
-      <c r="Z4">
-        <v>-0.41016333938294</v>
-      </c>
-      <c r="AA4">
-        <v>-0</v>
-      </c>
-      <c r="AB4">
-        <v>0.08436000882951943</v>
-      </c>
-      <c r="AC4">
-        <v>-0.08436000882951943</v>
-      </c>
-      <c r="AD4">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="AG4">
-        <v>-1723.2</v>
-      </c>
-      <c r="AH4">
-        <v>0.2494322482967449</v>
-      </c>
-      <c r="AI4">
-        <v>0.148892905558066</v>
-      </c>
-      <c r="AJ4">
-        <v>1.130041314184537</v>
-      </c>
-      <c r="AK4">
-        <v>1.279762346825102</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>
